--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/INDIANA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/INDIANA_2021.xlsx
@@ -445,7 +445,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="6">
@@ -607,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="D20">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="21">
@@ -733,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="22">
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="D22">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="25">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="26">
@@ -841,7 +841,7 @@
         <v>1</v>
       </c>
       <c r="D27">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="28">
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="31">
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="32">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="D36">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="37">
@@ -1021,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="D37">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="38">
@@ -1129,7 +1129,7 @@
         <v>1</v>
       </c>
       <c r="D43">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="44">
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="D44">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="45">
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="54">
@@ -1381,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="D57">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="58">
@@ -1399,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="D58">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="59">
@@ -1471,7 +1471,7 @@
         <v>1</v>
       </c>
       <c r="D62">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="63">
@@ -1489,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="D63">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="64">
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="D64">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="65">
@@ -1579,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="D68">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="69">
@@ -1633,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="72">
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="74">
@@ -1849,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="84">
@@ -1867,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="85">
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="88">
@@ -1939,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="89">
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="92">
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="94">
@@ -2155,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="101">
@@ -2191,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="103">
@@ -2209,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="104">
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="D106">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="107">
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="108">
@@ -2299,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="109">
@@ -2317,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="D109">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="110">
@@ -2335,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="D110">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="111">
@@ -2389,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="114">
@@ -2400,14 +2400,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="115">
@@ -2425,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="D115">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="116">
@@ -2461,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="D117">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="118">
@@ -2677,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="D129">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="130">
@@ -3199,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="D158">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="159">
@@ -3253,7 +3253,7 @@
         <v>1</v>
       </c>
       <c r="D161">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="162">
@@ -3541,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="D177">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="178">
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="D181">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="182">
@@ -3775,7 +3775,7 @@
         <v>1</v>
       </c>
       <c r="D190">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="191">
@@ -3793,7 +3793,7 @@
         <v>1</v>
       </c>
       <c r="D191">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="192">
@@ -3973,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="D201">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="202">
@@ -3991,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="D202">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="203">
@@ -4045,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="D205">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="206">
@@ -4099,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="D208">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="209">
@@ -4117,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="D209">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="210">
@@ -4135,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="D210">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="211">
@@ -4153,7 +4153,7 @@
         <v>1</v>
       </c>
       <c r="D211">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="212">
@@ -4189,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="D213">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="214">
@@ -4207,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="D214">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="215">
@@ -4243,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="D216">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="217">
@@ -4315,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="D220">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="221">
@@ -4351,7 +4351,7 @@
         <v>1</v>
       </c>
       <c r="D222">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="223">
@@ -4387,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="D224">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="225">
@@ -4441,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="D227">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="228">
@@ -4459,7 +4459,7 @@
         <v>1</v>
       </c>
       <c r="D228">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="229">
@@ -4549,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="D233">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="234">
@@ -4909,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="D253">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="254">
@@ -4945,7 +4945,7 @@
         <v>1</v>
       </c>
       <c r="D255">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="256">
@@ -4999,7 +4999,7 @@
         <v>10</v>
       </c>
       <c r="D258">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="259">
@@ -5017,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="D259">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="260">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C262">
@@ -5107,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="D264">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="265">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C270">
@@ -5683,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="D296">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="297">
@@ -5737,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="D299">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="300">
@@ -5809,7 +5809,7 @@
         <v>10</v>
       </c>
       <c r="D303">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="304">
@@ -5827,7 +5827,7 @@
         <v>10</v>
       </c>
       <c r="D304">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="305">
@@ -5863,7 +5863,7 @@
         <v>1</v>
       </c>
       <c r="D306">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="307">
@@ -5881,7 +5881,7 @@
         <v>1</v>
       </c>
       <c r="D307">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="308">
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="D308">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="309">
@@ -6025,7 +6025,7 @@
         <v>1</v>
       </c>
       <c r="D315">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="316">
@@ -6079,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="D318">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="319">
@@ -6115,7 +6115,7 @@
         <v>10</v>
       </c>
       <c r="D320">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="321">
@@ -6133,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="D321">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="322">
@@ -6277,7 +6277,7 @@
         <v>1</v>
       </c>
       <c r="D329">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="330">
@@ -6313,7 +6313,7 @@
         <v>10</v>
       </c>
       <c r="D331">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="332">
@@ -6511,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="D342">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="343">
@@ -6763,7 +6763,7 @@
         <v>1</v>
       </c>
       <c r="D356">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="357">
@@ -6817,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="D359">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="360">
@@ -6853,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="D361">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="362">
@@ -6871,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="D362">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="363">
@@ -6943,7 +6943,7 @@
         <v>1</v>
       </c>
       <c r="D366">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="367">
@@ -6961,7 +6961,7 @@
         <v>1</v>
       </c>
       <c r="D367">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="368">
@@ -7123,7 +7123,7 @@
         <v>1</v>
       </c>
       <c r="D376">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="377">
@@ -7141,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="D377">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="378">
@@ -7177,7 +7177,7 @@
         <v>1</v>
       </c>
       <c r="D379">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="380">
@@ -7195,7 +7195,7 @@
         <v>1</v>
       </c>
       <c r="D380">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="381">
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="D384">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="385">
@@ -7303,7 +7303,7 @@
         <v>1</v>
       </c>
       <c r="D386">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="387">
@@ -7357,7 +7357,7 @@
         <v>1</v>
       </c>
       <c r="D389">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="390">
@@ -7519,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="D398">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="399">
@@ -7537,7 +7537,7 @@
         <v>1</v>
       </c>
       <c r="D399">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="400">
@@ -7573,7 +7573,7 @@
         <v>1</v>
       </c>
       <c r="D401">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="402">
@@ -7663,7 +7663,7 @@
         <v>1</v>
       </c>
       <c r="D406">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="407">
@@ -7699,7 +7699,7 @@
         <v>1</v>
       </c>
       <c r="D408">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="409">
@@ -7735,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="D410">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="411">
@@ -7789,7 +7789,7 @@
         <v>1</v>
       </c>
       <c r="D413">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="414">
@@ -7807,7 +7807,7 @@
         <v>1</v>
       </c>
       <c r="D414">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="415">
@@ -7897,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="D419">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="420">
@@ -7915,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="D420">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="421">
@@ -8023,7 +8023,7 @@
         <v>1</v>
       </c>
       <c r="D426">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="427">
@@ -8131,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="D432">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="433">
@@ -8203,7 +8203,7 @@
         <v>1</v>
       </c>
       <c r="D436">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="437">
@@ -8221,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="D437">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="438">
@@ -8437,7 +8437,7 @@
         <v>101</v>
       </c>
       <c r="D449">
-        <v>0.009153525466739169</v>
+        <v>0.009153525466739167</v>
       </c>
     </row>
     <row r="450">
@@ -8473,7 +8473,7 @@
         <v>1</v>
       </c>
       <c r="D451">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="452">
@@ -8563,7 +8563,7 @@
         <v>1</v>
       </c>
       <c r="D456">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="457">
@@ -8617,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="D459">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="460">
@@ -8653,7 +8653,7 @@
         <v>1</v>
       </c>
       <c r="D461">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="462">
@@ -8707,7 +8707,7 @@
         <v>1</v>
       </c>
       <c r="D464">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="465">
@@ -8725,7 +8725,7 @@
         <v>1</v>
       </c>
       <c r="D465">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="466">
@@ -8743,7 +8743,7 @@
         <v>1</v>
       </c>
       <c r="D466">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="467">
@@ -8761,7 +8761,7 @@
         <v>1</v>
       </c>
       <c r="D467">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="468">
@@ -8815,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="D470">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="471">
@@ -8869,7 +8869,7 @@
         <v>1</v>
       </c>
       <c r="D473">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="474">
@@ -8887,7 +8887,7 @@
         <v>10</v>
       </c>
       <c r="D474">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="475">
@@ -8905,7 +8905,7 @@
         <v>1</v>
       </c>
       <c r="D475">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="476">
@@ -9013,7 +9013,7 @@
         <v>1</v>
       </c>
       <c r="D481">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="482">
@@ -9121,7 +9121,7 @@
         <v>1</v>
       </c>
       <c r="D487">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="488">
@@ -9157,7 +9157,7 @@
         <v>1</v>
       </c>
       <c r="D489">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="490">
@@ -9319,7 +9319,7 @@
         <v>1</v>
       </c>
       <c r="D498">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="499">
@@ -9463,7 +9463,7 @@
         <v>1</v>
       </c>
       <c r="D506">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="507">
@@ -9535,7 +9535,7 @@
         <v>1</v>
       </c>
       <c r="D510">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="511">
@@ -9553,7 +9553,7 @@
         <v>10</v>
       </c>
       <c r="D511">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="512">
@@ -9625,7 +9625,7 @@
         <v>1</v>
       </c>
       <c r="D515">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="516">
@@ -9643,7 +9643,7 @@
         <v>1</v>
       </c>
       <c r="D516">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="517">
@@ -9697,7 +9697,7 @@
         <v>1</v>
       </c>
       <c r="D519">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="520">
@@ -9715,7 +9715,7 @@
         <v>1</v>
       </c>
       <c r="D520">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="521">
@@ -9769,7 +9769,7 @@
         <v>1</v>
       </c>
       <c r="D523">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="524">
@@ -9823,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="D526">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="527">
@@ -9859,7 +9859,7 @@
         <v>1</v>
       </c>
       <c r="D528">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="529">
@@ -9913,7 +9913,7 @@
         <v>1</v>
       </c>
       <c r="D531">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="532">
@@ -9931,7 +9931,7 @@
         <v>1</v>
       </c>
       <c r="D532">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="533">
@@ -10381,7 +10381,7 @@
         <v>1</v>
       </c>
       <c r="D557">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="558">
@@ -10525,7 +10525,7 @@
         <v>10</v>
       </c>
       <c r="D565">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="566">
@@ -10597,7 +10597,7 @@
         <v>1</v>
       </c>
       <c r="D569">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="570">
@@ -10669,7 +10669,7 @@
         <v>1</v>
       </c>
       <c r="D573">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="574">
@@ -10741,7 +10741,7 @@
         <v>1</v>
       </c>
       <c r="D577">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="578">
@@ -10759,7 +10759,7 @@
         <v>10</v>
       </c>
       <c r="D578">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="579">
@@ -10939,7 +10939,7 @@
         <v>1</v>
       </c>
       <c r="D588">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="589">
@@ -11137,7 +11137,7 @@
         <v>1</v>
       </c>
       <c r="D599">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="600">
@@ -11209,7 +11209,7 @@
         <v>1</v>
       </c>
       <c r="D603">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="604">
@@ -11353,7 +11353,7 @@
         <v>1</v>
       </c>
       <c r="D611">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="612">
@@ -11371,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="D612">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="613">
@@ -11407,7 +11407,7 @@
         <v>1</v>
       </c>
       <c r="D614">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="615">
@@ -11497,7 +11497,7 @@
         <v>1</v>
       </c>
       <c r="D619">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="620">
@@ -11533,7 +11533,7 @@
         <v>1</v>
       </c>
       <c r="D621">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="622">
@@ -11569,7 +11569,7 @@
         <v>1</v>
       </c>
       <c r="D623">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="624">
@@ -11605,7 +11605,7 @@
         <v>1</v>
       </c>
       <c r="D625">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="626">
@@ -11623,7 +11623,7 @@
         <v>1</v>
       </c>
       <c r="D626">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="627">
@@ -11641,7 +11641,7 @@
         <v>1</v>
       </c>
       <c r="D627">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="628">
@@ -11659,7 +11659,7 @@
         <v>1</v>
       </c>
       <c r="D628">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="629">
@@ -11767,7 +11767,7 @@
         <v>1</v>
       </c>
       <c r="D634">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="635">
@@ -11803,7 +11803,7 @@
         <v>1</v>
       </c>
       <c r="D636">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="637">
@@ -11965,7 +11965,7 @@
         <v>10</v>
       </c>
       <c r="D645">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="646">
@@ -11983,7 +11983,7 @@
         <v>1</v>
       </c>
       <c r="D646">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="647">
@@ -12055,7 +12055,7 @@
         <v>1</v>
       </c>
       <c r="D650">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="651">
@@ -12109,7 +12109,7 @@
         <v>1</v>
       </c>
       <c r="D653">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="654">
@@ -12163,7 +12163,7 @@
         <v>1</v>
       </c>
       <c r="D656">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="657">
@@ -12235,7 +12235,7 @@
         <v>1</v>
       </c>
       <c r="D660">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="661">
@@ -12361,7 +12361,7 @@
         <v>1</v>
       </c>
       <c r="D667">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="668">
@@ -12397,7 +12397,7 @@
         <v>10</v>
       </c>
       <c r="D669">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="670">
@@ -12415,7 +12415,7 @@
         <v>1</v>
       </c>
       <c r="D670">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="671">
@@ -12487,7 +12487,7 @@
         <v>1</v>
       </c>
       <c r="D674">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="675">
@@ -12505,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="D675">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="676">
@@ -12541,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="D677">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="678">
@@ -12559,7 +12559,7 @@
         <v>1</v>
       </c>
       <c r="D678">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="679">
@@ -12577,7 +12577,7 @@
         <v>1</v>
       </c>
       <c r="D679">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="680">
@@ -12595,7 +12595,7 @@
         <v>1</v>
       </c>
       <c r="D680">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="681">
@@ -12613,7 +12613,7 @@
         <v>1</v>
       </c>
       <c r="D681">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="682">
@@ -12631,7 +12631,7 @@
         <v>1</v>
       </c>
       <c r="D682">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="683">
@@ -12685,7 +12685,7 @@
         <v>1</v>
       </c>
       <c r="D685">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="686">
@@ -12757,7 +12757,7 @@
         <v>1</v>
       </c>
       <c r="D689">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="690">
@@ -12811,7 +12811,7 @@
         <v>1</v>
       </c>
       <c r="D692">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="693">
@@ -12829,7 +12829,7 @@
         <v>1</v>
       </c>
       <c r="D693">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="694">
@@ -12847,7 +12847,7 @@
         <v>1</v>
       </c>
       <c r="D694">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="695">
@@ -12865,7 +12865,7 @@
         <v>1</v>
       </c>
       <c r="D695">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="696">
@@ -12883,7 +12883,7 @@
         <v>1</v>
       </c>
       <c r="D696">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="697">
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="D697">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="698">
@@ -12919,7 +12919,7 @@
         <v>1</v>
       </c>
       <c r="D698">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="699">
@@ -12937,7 +12937,7 @@
         <v>1</v>
       </c>
       <c r="D699">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="700">
@@ -12973,7 +12973,7 @@
         <v>1</v>
       </c>
       <c r="D701">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="702">
@@ -12991,7 +12991,7 @@
         <v>1</v>
       </c>
       <c r="D702">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="703">
@@ -13009,7 +13009,7 @@
         <v>1</v>
       </c>
       <c r="D703">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="704">
@@ -13027,7 +13027,7 @@
         <v>1</v>
       </c>
       <c r="D704">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="705">
@@ -13045,7 +13045,7 @@
         <v>1</v>
       </c>
       <c r="D705">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="706">
@@ -13063,7 +13063,7 @@
         <v>1</v>
       </c>
       <c r="D706">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="707">
@@ -13099,7 +13099,7 @@
         <v>1</v>
       </c>
       <c r="D708">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="709">
@@ -13135,7 +13135,7 @@
         <v>1</v>
       </c>
       <c r="D710">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="711">
@@ -13153,7 +13153,7 @@
         <v>1</v>
       </c>
       <c r="D711">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="712">
@@ -13171,7 +13171,7 @@
         <v>1</v>
       </c>
       <c r="D712">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="713">
@@ -13261,7 +13261,7 @@
         <v>1</v>
       </c>
       <c r="D717">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="718">
@@ -13279,7 +13279,7 @@
         <v>10</v>
       </c>
       <c r="D718">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="719">
@@ -13297,7 +13297,7 @@
         <v>1</v>
       </c>
       <c r="D719">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="720">
@@ -13315,7 +13315,7 @@
         <v>1</v>
       </c>
       <c r="D720">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="721">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C723">
@@ -13423,7 +13423,7 @@
         <v>1</v>
       </c>
       <c r="D726">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="727">
@@ -13441,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="D727">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="728">
@@ -13459,7 +13459,7 @@
         <v>1</v>
       </c>
       <c r="D728">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="729">
@@ -13495,7 +13495,7 @@
         <v>1</v>
       </c>
       <c r="D730">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="731">
@@ -13549,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="D733">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="734">
@@ -13567,7 +13567,7 @@
         <v>1</v>
       </c>
       <c r="D734">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="735">
@@ -13585,7 +13585,7 @@
         <v>1</v>
       </c>
       <c r="D735">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="736">
@@ -13603,7 +13603,7 @@
         <v>1</v>
       </c>
       <c r="D736">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="737">
@@ -13621,7 +13621,7 @@
         <v>1</v>
       </c>
       <c r="D737">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="738">
@@ -13639,7 +13639,7 @@
         <v>1</v>
       </c>
       <c r="D738">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="739">
@@ -13657,7 +13657,7 @@
         <v>1</v>
       </c>
       <c r="D739">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="740">
@@ -13675,7 +13675,7 @@
         <v>1</v>
       </c>
       <c r="D740">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="741">
@@ -13711,7 +13711,7 @@
         <v>1</v>
       </c>
       <c r="D742">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="743">
@@ -13747,7 +13747,7 @@
         <v>1</v>
       </c>
       <c r="D744">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="745">
@@ -13783,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="D746">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="747">
@@ -13801,7 +13801,7 @@
         <v>1</v>
       </c>
       <c r="D747">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="748">
@@ -13819,7 +13819,7 @@
         <v>1</v>
       </c>
       <c r="D748">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="749">
@@ -13837,7 +13837,7 @@
         <v>1</v>
       </c>
       <c r="D749">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="750">
@@ -13855,7 +13855,7 @@
         <v>1</v>
       </c>
       <c r="D750">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="751">
@@ -13873,7 +13873,7 @@
         <v>1</v>
       </c>
       <c r="D751">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="752">
@@ -13891,7 +13891,7 @@
         <v>1</v>
       </c>
       <c r="D752">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="753">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C754">
@@ -13981,7 +13981,7 @@
         <v>1</v>
       </c>
       <c r="D757">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="758">
@@ -13999,7 +13999,7 @@
         <v>1</v>
       </c>
       <c r="D758">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="759">
@@ -14010,14 +14010,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C759">
         <v>1</v>
       </c>
       <c r="D759">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="760">
@@ -14035,7 +14035,7 @@
         <v>1</v>
       </c>
       <c r="D760">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="761">
@@ -14071,7 +14071,7 @@
         <v>1</v>
       </c>
       <c r="D762">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="763">
@@ -14089,7 +14089,7 @@
         <v>1</v>
       </c>
       <c r="D763">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="764">
@@ -14125,7 +14125,7 @@
         <v>1</v>
       </c>
       <c r="D765">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="766">
@@ -14143,7 +14143,7 @@
         <v>1</v>
       </c>
       <c r="D766">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="767">
@@ -14161,7 +14161,7 @@
         <v>1</v>
       </c>
       <c r="D767">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="768">
@@ -14197,7 +14197,7 @@
         <v>1</v>
       </c>
       <c r="D769">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="770">
@@ -14233,7 +14233,7 @@
         <v>1</v>
       </c>
       <c r="D771">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="772">
@@ -14251,7 +14251,7 @@
         <v>1</v>
       </c>
       <c r="D772">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="773">
@@ -14341,7 +14341,7 @@
         <v>1</v>
       </c>
       <c r="D777">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="778">
@@ -14377,7 +14377,7 @@
         <v>1</v>
       </c>
       <c r="D779">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="780">
@@ -14467,7 +14467,7 @@
         <v>1</v>
       </c>
       <c r="D784">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="785">
@@ -14503,7 +14503,7 @@
         <v>1</v>
       </c>
       <c r="D786">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="787">
@@ -14539,7 +14539,7 @@
         <v>1</v>
       </c>
       <c r="D788">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="789">
@@ -14575,7 +14575,7 @@
         <v>1</v>
       </c>
       <c r="D790">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="791">
@@ -14647,7 +14647,7 @@
         <v>1</v>
       </c>
       <c r="D794">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="795">
@@ -14683,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="D796">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="797">
@@ -14791,7 +14791,7 @@
         <v>1</v>
       </c>
       <c r="D802">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="803">
@@ -14809,7 +14809,7 @@
         <v>1</v>
       </c>
       <c r="D803">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="804">
@@ -14827,7 +14827,7 @@
         <v>1</v>
       </c>
       <c r="D804">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="805">
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="D806">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="807">
@@ -14881,7 +14881,7 @@
         <v>1</v>
       </c>
       <c r="D807">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="808">
@@ -14899,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="D808">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="809">
@@ -14953,7 +14953,7 @@
         <v>1</v>
       </c>
       <c r="D811">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="812">
@@ -14989,7 +14989,7 @@
         <v>1</v>
       </c>
       <c r="D813">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="814">
@@ -15007,7 +15007,7 @@
         <v>1</v>
       </c>
       <c r="D814">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="815">
@@ -15061,7 +15061,7 @@
         <v>1</v>
       </c>
       <c r="D817">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="818">
@@ -15097,7 +15097,7 @@
         <v>1</v>
       </c>
       <c r="D819">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="820">
@@ -15133,7 +15133,7 @@
         <v>10</v>
       </c>
       <c r="D821">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="822">
@@ -15169,7 +15169,7 @@
         <v>1</v>
       </c>
       <c r="D823">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="824">
@@ -15241,7 +15241,7 @@
         <v>1</v>
       </c>
       <c r="D827">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="828">
@@ -15259,7 +15259,7 @@
         <v>1</v>
       </c>
       <c r="D828">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="829">
@@ -15295,7 +15295,7 @@
         <v>1</v>
       </c>
       <c r="D830">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="831">
@@ -15331,7 +15331,7 @@
         <v>1</v>
       </c>
       <c r="D832">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="833">
@@ -15457,7 +15457,7 @@
         <v>1</v>
       </c>
       <c r="D839">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="840">
@@ -15511,7 +15511,7 @@
         <v>1</v>
       </c>
       <c r="D842">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="843">
@@ -15547,7 +15547,7 @@
         <v>1</v>
       </c>
       <c r="D844">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="845">
@@ -15565,7 +15565,7 @@
         <v>1</v>
       </c>
       <c r="D845">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="846">
@@ -15583,7 +15583,7 @@
         <v>1</v>
       </c>
       <c r="D846">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="847">
@@ -15619,7 +15619,7 @@
         <v>1</v>
       </c>
       <c r="D848">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="849">
@@ -15727,7 +15727,7 @@
         <v>1</v>
       </c>
       <c r="D854">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="855">
@@ -15763,7 +15763,7 @@
         <v>1</v>
       </c>
       <c r="D856">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="857">
@@ -15835,7 +15835,7 @@
         <v>1</v>
       </c>
       <c r="D860">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="861">
@@ -15907,7 +15907,7 @@
         <v>10</v>
       </c>
       <c r="D864">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="865">
@@ -15943,7 +15943,7 @@
         <v>1</v>
       </c>
       <c r="D866">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="867">
@@ -16033,7 +16033,7 @@
         <v>1</v>
       </c>
       <c r="D871">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="872">
@@ -16177,7 +16177,7 @@
         <v>1</v>
       </c>
       <c r="D879">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="880">
@@ -16213,7 +16213,7 @@
         <v>1</v>
       </c>
       <c r="D881">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="882">
@@ -16285,7 +16285,7 @@
         <v>1</v>
       </c>
       <c r="D885">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="886">
@@ -16303,7 +16303,7 @@
         <v>1</v>
       </c>
       <c r="D886">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="887">
@@ -16321,7 +16321,7 @@
         <v>1</v>
       </c>
       <c r="D887">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="888">
@@ -16339,7 +16339,7 @@
         <v>1</v>
       </c>
       <c r="D888">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="889">
@@ -16375,7 +16375,7 @@
         <v>1</v>
       </c>
       <c r="D890">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="891">
@@ -16393,7 +16393,7 @@
         <v>1</v>
       </c>
       <c r="D891">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="892">
@@ -16519,7 +16519,7 @@
         <v>1</v>
       </c>
       <c r="D898">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="899">
@@ -16609,7 +16609,7 @@
         <v>1</v>
       </c>
       <c r="D903">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="904">
@@ -16735,7 +16735,7 @@
         <v>1</v>
       </c>
       <c r="D910">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="911">
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="D912">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="913">
@@ -16807,7 +16807,7 @@
         <v>10</v>
       </c>
       <c r="D914">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="915">
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="D915">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="916">
@@ -16915,7 +16915,7 @@
         <v>1</v>
       </c>
       <c r="D920">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="921">
@@ -16933,7 +16933,7 @@
         <v>1</v>
       </c>
       <c r="D921">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="922">
@@ -16951,7 +16951,7 @@
         <v>10</v>
       </c>
       <c r="D922">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="923">
@@ -16987,7 +16987,7 @@
         <v>1</v>
       </c>
       <c r="D924">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="925">
@@ -17167,7 +17167,7 @@
         <v>1</v>
       </c>
       <c r="D934">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="935">
@@ -17185,7 +17185,7 @@
         <v>1</v>
       </c>
       <c r="D935">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="936">
@@ -17275,7 +17275,7 @@
         <v>1</v>
       </c>
       <c r="D940">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="941">
@@ -17401,7 +17401,7 @@
         <v>1</v>
       </c>
       <c r="D947">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="948">
@@ -17455,7 +17455,7 @@
         <v>1</v>
       </c>
       <c r="D950">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="951">
@@ -17509,7 +17509,7 @@
         <v>1</v>
       </c>
       <c r="D953">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="954">
@@ -17617,7 +17617,7 @@
         <v>1</v>
       </c>
       <c r="D959">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="960">
@@ -17653,7 +17653,7 @@
         <v>10</v>
       </c>
       <c r="D961">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="962">
@@ -17689,7 +17689,7 @@
         <v>1</v>
       </c>
       <c r="D963">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="964">
@@ -17833,7 +17833,7 @@
         <v>1</v>
       </c>
       <c r="D971">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="972">
@@ -17851,7 +17851,7 @@
         <v>1</v>
       </c>
       <c r="D972">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="973">
@@ -17887,7 +17887,7 @@
         <v>1</v>
       </c>
       <c r="D974">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="975">
@@ -17923,7 +17923,7 @@
         <v>1</v>
       </c>
       <c r="D976">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="977">
@@ -18013,7 +18013,7 @@
         <v>1</v>
       </c>
       <c r="D981">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="982">
@@ -18139,7 +18139,7 @@
         <v>1</v>
       </c>
       <c r="D988">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="989">
@@ -18175,7 +18175,7 @@
         <v>1</v>
       </c>
       <c r="D990">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="991">
@@ -18211,7 +18211,7 @@
         <v>1</v>
       </c>
       <c r="D992">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="993">
@@ -18247,7 +18247,7 @@
         <v>1</v>
       </c>
       <c r="D994">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="995">
@@ -18283,7 +18283,7 @@
         <v>1</v>
       </c>
       <c r="D996">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="997">
@@ -18301,7 +18301,7 @@
         <v>1</v>
       </c>
       <c r="D997">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="998">
@@ -18319,7 +18319,7 @@
         <v>1</v>
       </c>
       <c r="D998">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="999">
@@ -18337,7 +18337,7 @@
         <v>1</v>
       </c>
       <c r="D999">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1000">
@@ -18355,7 +18355,7 @@
         <v>1</v>
       </c>
       <c r="D1000">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1001">
@@ -18373,7 +18373,7 @@
         <v>1</v>
       </c>
       <c r="D1001">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1002">
@@ -18391,7 +18391,7 @@
         <v>1</v>
       </c>
       <c r="D1002">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1003">
@@ -18409,7 +18409,7 @@
         <v>1</v>
       </c>
       <c r="D1003">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1004">
@@ -18499,7 +18499,7 @@
         <v>1</v>
       </c>
       <c r="D1008">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1009">
@@ -18535,7 +18535,7 @@
         <v>1</v>
       </c>
       <c r="D1010">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1011">
@@ -18589,7 +18589,7 @@
         <v>1</v>
       </c>
       <c r="D1013">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1014">
@@ -18625,7 +18625,7 @@
         <v>1</v>
       </c>
       <c r="D1015">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1016">
@@ -18643,7 +18643,7 @@
         <v>1</v>
       </c>
       <c r="D1016">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1017">
@@ -18769,7 +18769,7 @@
         <v>1</v>
       </c>
       <c r="D1023">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1024">
@@ -18787,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="D1024">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1025">
@@ -18877,7 +18877,7 @@
         <v>1</v>
       </c>
       <c r="D1029">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1030">
@@ -18985,7 +18985,7 @@
         <v>1</v>
       </c>
       <c r="D1035">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1036">
@@ -19111,7 +19111,7 @@
         <v>10</v>
       </c>
       <c r="D1042">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="1043">
@@ -19147,7 +19147,7 @@
         <v>1</v>
       </c>
       <c r="D1044">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1045">
@@ -19165,7 +19165,7 @@
         <v>1</v>
       </c>
       <c r="D1045">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1046">
@@ -19219,7 +19219,7 @@
         <v>1</v>
       </c>
       <c r="D1048">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1049">
@@ -19237,7 +19237,7 @@
         <v>1</v>
       </c>
       <c r="D1049">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1050">
@@ -19255,7 +19255,7 @@
         <v>1</v>
       </c>
       <c r="D1050">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1051">
@@ -19309,7 +19309,7 @@
         <v>1</v>
       </c>
       <c r="D1053">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1054">
@@ -19327,7 +19327,7 @@
         <v>1</v>
       </c>
       <c r="D1054">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1055">
@@ -19345,7 +19345,7 @@
         <v>1</v>
       </c>
       <c r="D1055">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1056">
@@ -19381,7 +19381,7 @@
         <v>1</v>
       </c>
       <c r="D1057">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1058">
@@ -19399,7 +19399,7 @@
         <v>1</v>
       </c>
       <c r="D1058">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1059">
@@ -19435,7 +19435,7 @@
         <v>1</v>
       </c>
       <c r="D1060">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1061">
@@ -19525,7 +19525,7 @@
         <v>1</v>
       </c>
       <c r="D1065">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1066">
@@ -19615,7 +19615,7 @@
         <v>1</v>
       </c>
       <c r="D1070">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1071">
@@ -19669,7 +19669,7 @@
         <v>1</v>
       </c>
       <c r="D1073">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1074">
@@ -19723,7 +19723,7 @@
         <v>1</v>
       </c>
       <c r="D1076">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1077">
@@ -19741,7 +19741,7 @@
         <v>1</v>
       </c>
       <c r="D1077">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1078">
@@ -19759,7 +19759,7 @@
         <v>1</v>
       </c>
       <c r="D1078">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1079">
@@ -19831,7 +19831,7 @@
         <v>1</v>
       </c>
       <c r="D1082">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1083">
@@ -19849,7 +19849,7 @@
         <v>10</v>
       </c>
       <c r="D1083">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="1084">
@@ -19885,7 +19885,7 @@
         <v>1</v>
       </c>
       <c r="D1085">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1086">
@@ -19939,7 +19939,7 @@
         <v>1</v>
       </c>
       <c r="D1088">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1089">
@@ -19993,7 +19993,7 @@
         <v>1</v>
       </c>
       <c r="D1091">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1092">
@@ -20083,7 +20083,7 @@
         <v>1</v>
       </c>
       <c r="D1096">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1097">
@@ -20101,7 +20101,7 @@
         <v>1</v>
       </c>
       <c r="D1097">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1098">
@@ -20119,7 +20119,7 @@
         <v>1</v>
       </c>
       <c r="D1098">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1099">
@@ -20137,7 +20137,7 @@
         <v>1</v>
       </c>
       <c r="D1099">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1100">
@@ -20191,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="D1102">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1103">
@@ -20209,7 +20209,7 @@
         <v>1</v>
       </c>
       <c r="D1103">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1104">
@@ -20317,7 +20317,7 @@
         <v>1</v>
       </c>
       <c r="D1109">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1110">
@@ -20407,7 +20407,7 @@
         <v>1</v>
       </c>
       <c r="D1114">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1115">
@@ -20425,7 +20425,7 @@
         <v>1</v>
       </c>
       <c r="D1115">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1116">
@@ -20497,7 +20497,7 @@
         <v>1</v>
       </c>
       <c r="D1119">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1120">
@@ -20515,7 +20515,7 @@
         <v>1</v>
       </c>
       <c r="D1120">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1121">
@@ -20587,7 +20587,7 @@
         <v>1</v>
       </c>
       <c r="D1124">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1125">
@@ -20605,7 +20605,7 @@
         <v>1</v>
       </c>
       <c r="D1125">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1126">
@@ -20641,7 +20641,7 @@
         <v>1</v>
       </c>
       <c r="D1127">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1128">
@@ -20695,7 +20695,7 @@
         <v>1</v>
       </c>
       <c r="D1130">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1131">
@@ -20731,7 +20731,7 @@
         <v>1</v>
       </c>
       <c r="D1132">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1133">
@@ -20821,7 +20821,7 @@
         <v>1</v>
       </c>
       <c r="D1137">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1138">
@@ -20893,7 +20893,7 @@
         <v>1</v>
       </c>
       <c r="D1141">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1142">
@@ -20911,7 +20911,7 @@
         <v>1</v>
       </c>
       <c r="D1142">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1143">
@@ -20929,7 +20929,7 @@
         <v>1</v>
       </c>
       <c r="D1143">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1144">
@@ -21055,7 +21055,7 @@
         <v>1</v>
       </c>
       <c r="D1150">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1151">
@@ -21073,7 +21073,7 @@
         <v>1</v>
       </c>
       <c r="D1151">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1152">
@@ -21181,7 +21181,7 @@
         <v>1</v>
       </c>
       <c r="D1157">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1158">
@@ -21523,7 +21523,7 @@
         <v>1</v>
       </c>
       <c r="D1176">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1177">
@@ -21541,7 +21541,7 @@
         <v>1</v>
       </c>
       <c r="D1177">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1178">
@@ -21595,7 +21595,7 @@
         <v>1</v>
       </c>
       <c r="D1180">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1181">
@@ -21685,7 +21685,7 @@
         <v>1</v>
       </c>
       <c r="D1185">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1186">
@@ -21703,7 +21703,7 @@
         <v>1</v>
       </c>
       <c r="D1186">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1187">
@@ -21721,7 +21721,7 @@
         <v>1</v>
       </c>
       <c r="D1187">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1188">
@@ -21793,7 +21793,7 @@
         <v>1</v>
       </c>
       <c r="D1191">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1192">
@@ -21883,7 +21883,7 @@
         <v>1</v>
       </c>
       <c r="D1196">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1197">
@@ -21901,7 +21901,7 @@
         <v>1</v>
       </c>
       <c r="D1197">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1198">
@@ -21919,7 +21919,7 @@
         <v>1</v>
       </c>
       <c r="D1198">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1199">
@@ -21937,7 +21937,7 @@
         <v>1</v>
       </c>
       <c r="D1199">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1200">
@@ -21955,7 +21955,7 @@
         <v>1</v>
       </c>
       <c r="D1200">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1201">
@@ -22045,7 +22045,7 @@
         <v>1</v>
       </c>
       <c r="D1205">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1206">
@@ -22207,7 +22207,7 @@
         <v>1</v>
       </c>
       <c r="D1214">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1215">
@@ -22243,7 +22243,7 @@
         <v>1</v>
       </c>
       <c r="D1216">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1217">
@@ -22279,7 +22279,7 @@
         <v>1</v>
       </c>
       <c r="D1218">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1219">
@@ -22315,7 +22315,7 @@
         <v>1</v>
       </c>
       <c r="D1220">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1221">
@@ -22459,7 +22459,7 @@
         <v>1</v>
       </c>
       <c r="D1228">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1229">
@@ -22477,7 +22477,7 @@
         <v>1</v>
       </c>
       <c r="D1229">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1230">
@@ -22495,7 +22495,7 @@
         <v>1</v>
       </c>
       <c r="D1230">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1231">
@@ -22513,7 +22513,7 @@
         <v>1</v>
       </c>
       <c r="D1231">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1232">
@@ -22567,7 +22567,7 @@
         <v>1</v>
       </c>
       <c r="D1234">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1235">
@@ -22585,7 +22585,7 @@
         <v>1</v>
       </c>
       <c r="D1235">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1236">
@@ -22639,7 +22639,7 @@
         <v>1</v>
       </c>
       <c r="D1238">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1239">
@@ -22657,7 +22657,7 @@
         <v>1</v>
       </c>
       <c r="D1239">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1240">
@@ -22675,7 +22675,7 @@
         <v>1</v>
       </c>
       <c r="D1240">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1241">
@@ -22693,7 +22693,7 @@
         <v>1</v>
       </c>
       <c r="D1241">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1242">
@@ -22729,7 +22729,7 @@
         <v>1</v>
       </c>
       <c r="D1243">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1244">
@@ -22963,7 +22963,7 @@
         <v>10</v>
       </c>
       <c r="D1256">
-        <v>0.0009062896501721951</v>
+        <v>0.0009062896501721952</v>
       </c>
     </row>
     <row r="1257">
@@ -23053,7 +23053,7 @@
         <v>1</v>
       </c>
       <c r="D1261">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1262">
@@ -23071,7 +23071,7 @@
         <v>1</v>
       </c>
       <c r="D1262">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1263">
@@ -23233,7 +23233,7 @@
         <v>1</v>
       </c>
       <c r="D1271">
-        <v>9.062896501721951E-05</v>
+        <v>9.062896501721952E-05</v>
       </c>
     </row>
     <row r="1272">
